--- a/2026_project/1_raw/storage.xlsx
+++ b/2026_project/1_raw/storage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutka\MT\AdOpT-NET0_dw\2026_project\1_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AC6353-1A48-4EA0-A908-F43616D1306D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C38139-35AA-4409-9B4C-2EFE9FDF48E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="15500" xr2:uid="{9826EF64-3551-444B-B13B-2294A2FF1464}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9826EF64-3551-444B-B13B-2294A2FF1464}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,9 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    https://www.gem.wiki/Porto_Corsini_E_Gas_Field_(Italy)#:~:text=Table%203:%20Field%2Dlevel%20location%20details%20for%20Porto,Concession/Block%2C%20Basin%2C%20Location%2C%20Onshore/Offshore%2C%20Coordinates%20(WGS%2084).</t>
+    https://www.gem.wiki/Porto_Corsini_E_Gas_Field_(Italy)#:~:text=Table%203:%20Field%2Dlevel%20location%20details%20for%20Porto,Concession/Block%2C%20Basin%2C%20Location%2C%20Onshore/Offshore%2C%20Coordinates%20(WGS%2084).
+Reply:
+    https://unmig.mase.gov.it/webgis-unmig/</t>
       </text>
     </comment>
     <comment ref="J4" authorId="6" shapeId="0" xr:uid="{8C1EE284-D6BE-4B2E-861C-F2ABCEC4B578}">
@@ -286,7 +288,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="456">
   <si>
     <t>ES</t>
   </si>
@@ -1651,6 +1653,9 @@
   </si>
   <si>
     <t>iso2</t>
+  </si>
+  <si>
+    <t>EU PCI, Article_G10</t>
   </si>
 </sst>
 </file>
@@ -1819,7 +1824,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -2210,6 +2215,15 @@
       </x:ext>
     </extLst>
   </threadedComment>
+  <threadedComment ref="J3" dT="2026-06-05T14:41:05.32" personId="{B5ED0D4A-F90C-4ACA-BF25-D90D88240A26}" id="{2DD3C940-F93D-4FF6-B568-F631D5D8E256}" parentId="{4C082E99-BACC-47F0-85AB-07E9AB14F766}">
+    <text>https://unmig.mase.gov.it/webgis-unmig/</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1995720397</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="39" url="https://unmig.mase.gov.it/webgis-unmig/"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
   <threadedComment ref="J4" dT="2026-02-06T23:54:56.53" personId="{B5ED0D4A-F90C-4ACA-BF25-D90D88240A26}" id="{8C1EE284-D6BE-4B2E-861C-F2ABCEC4B578}">
     <text>Casablanca field</text>
   </threadedComment>
@@ -2297,7 +2311,7 @@
   <dimension ref="A1:AP635"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.81640625" customWidth="1"/>
+    <col min="1" max="1" width="26.08984375" customWidth="1"/>
     <col min="2" max="2" width="9.08984375" customWidth="1"/>
     <col min="3" max="3" width="24.36328125" style="23" customWidth="1"/>
     <col min="4" max="4" width="13.36328125" style="22" customWidth="1"/>
@@ -2468,7 +2482,7 @@
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>349</v>
+        <v>455</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>3</v>
@@ -2525,7 +2539,7 @@
         <v>2029</v>
       </c>
       <c r="Y2" s="1">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD2" s="13" t="s">
         <v>352</v>
@@ -2631,7 +2645,7 @@
         <v>430</v>
       </c>
       <c r="E4" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="19">
         <v>1</v>
@@ -2732,7 +2746,7 @@
         <v>452</v>
       </c>
       <c r="E6" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="10">
         <v>2</v>
@@ -2785,7 +2799,7 @@
         <v>452</v>
       </c>
       <c r="E7" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="10">
         <v>2</v>
